--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2061-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2061-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17F79153-8BB6-4B27-B800-58EB263EE147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5553ACF8-E8D0-498F-A07A-B79CA40CAAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FA5B009F-E4A4-4E7B-BEA4-AF83A09E7AA6}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{30659E59-87F5-4F65-B2BE-3011D34B3437}"/>
   </bookViews>
   <sheets>
     <sheet name="2061-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1481,26 +1481,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7087AD31-1479-4B99-9BFA-4303D32DC0DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B55D0A-F2C4-44A4-A1DE-82962A6DE079}">
   <dimension ref="A1:R51"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="10.75" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1528,7 +1528,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1558,7 +1558,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1654,7 +1654,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>26</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="38">
         <v>2024</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2023</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2022</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>26</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>26</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2021</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>26</v>
       </c>
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>26</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2020</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2019</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2018</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2017</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2016</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>2015</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>2014</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>2013</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>2012</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>2011</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>2010</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40">
         <v>2009</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="38">
         <v>2008</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>2.2599999999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="40">
         <v>2007</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="38">
         <v>2006</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>1.91</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="40">
         <v>2005</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>7.19</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="38" t="s">
         <v>45</v>
       </c>
